--- a/output/pdf_financials_xlsx/VQS.xlsx
+++ b/output/pdf_financials_xlsx/VQS.xlsx
@@ -431,6 +431,15 @@
   </sheetPr>
   <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/VQS.xlsx
+++ b/output/pdf_financials_xlsx/VQS.xlsx
@@ -676,22 +676,22 @@
         <v>13.863734</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17.961333</v>
+        <v>28.239594</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.092108</v>
+        <v>33.657981</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.734115</v>
+        <v>31.241339</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.679589</v>
+        <v>32.612432</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.650551</v>
+        <v>26.259512</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.740233</v>
+        <v>33.945497</v>
       </c>
     </row>
     <row r="11">
@@ -704,22 +704,22 @@
         <v>-3.043747</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.811077</v>
+        <v>-12.089338</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13.830851</v>
+        <v>-18.735022</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>21.191588</v>
+        <v>-9.315636</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>17.432483</v>
+        <v>-14.50036</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>18.577547</v>
+        <v>-7.031414</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>19.633095</v>
+        <v>-13.572169</v>
       </c>
     </row>
     <row r="12">
@@ -1352,25 +1352,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.707654</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>16.835671</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>10.583534</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.657571</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.621778</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.573341</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.573341</v>
       </c>
     </row>
     <row r="35">
@@ -1408,25 +1408,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.707654</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>16.835671</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>10.583534</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.657571</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.621778</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.573341</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.573341</v>
       </c>
     </row>
     <row r="37">
@@ -1744,25 +1744,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.061406</v>
+        <v>3.353752</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>21.565652</v>
+        <v>4.729981</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>29.684196</v>
+        <v>19.100662</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.11863</v>
+        <v>7.461059</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.640795</v>
+        <v>6.019017</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>6.525536</v>
+        <v>4.952195</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.525536</v>
+        <v>4.952195</v>
       </c>
     </row>
     <row r="49">
@@ -3868,7 +3868,7 @@
         <v>-0.983479</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>-0.838031</v>
+        <v>0.6597730000000001</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>-1.070275</v>
@@ -3896,7 +3896,7 @@
         <v>0.9415210000000001</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>3.989144</v>
+        <v>5.486948</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>-1.070275</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
@@ -20109,7 +20109,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" s="5" t="n">

--- a/output/pdf_financials_xlsx/VQS.xlsx
+++ b/output/pdf_financials_xlsx/VQS.xlsx
@@ -844,13 +844,13 @@
         <v>-4.623353</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-10.201274</v>
+        <v>-12.089338</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-19.678749</v>
+        <v>-18.735022</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-8.811271</v>
+        <v>-9.315636</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-14.50036</v>
@@ -872,13 +872,13 @@
         <v>0.09915499999999999</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.944032</v>
+        <v>0.944032</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.943727</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.105256</v>
+        <v>0.609621</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>0.169164</v>
@@ -1180,13 +1180,13 @@
         <v>-4.623353</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-10.201274</v>
+        <v>-12.089338</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-19.678749</v>
+        <v>-18.735022</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.811271</v>
+        <v>-9.315636</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-14.50036</v>
@@ -1236,13 +1236,13 @@
         <v>-4.094869</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.755279</v>
+        <v>-11.643343</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-19.42165</v>
+        <v>-18.477923</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.232022000000001</v>
+        <v>-8.736387000000001</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-13.705256</v>
@@ -1264,13 +1264,13 @@
         <v>-16.31661916167111</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-30.72558528361203</v>
+        <v>-36.67230105185584</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-62.55602024452623</v>
+        <v>-59.51632972815373</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-17.95662409301785</v>
+        <v>-19.0568024830507</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-33.40787827152207</v>
@@ -1292,13 +1292,13 @@
         <v>-2.144655621147682</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-9.25405983605577</v>
+        <v>-7.808798132701725</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.037234543946625</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-1.194560920893251</v>
+        <v>-6.544062047937468</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-1.166619311520542</v>
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.141582</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.366077</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>1.487255</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.7485849999999999</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.782955</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.85405</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.925345</v>
       </c>
     </row>
     <row r="41">
@@ -1548,25 +1548,25 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.141582</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>0.366077</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0</v>
+        <v>1.487255</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.7485849999999999</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.782955</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.85405</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>0.925345</v>
       </c>
     </row>
     <row r="42">
@@ -1744,25 +1744,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.353752</v>
+        <v>3.21217</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.729981</v>
+        <v>4.363904</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>19.100662</v>
+        <v>17.613407</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7.461059</v>
+        <v>6.712474</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.019017</v>
+        <v>5.236062</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.952195</v>
+        <v>4.098145</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.952195</v>
+        <v>4.02685</v>
       </c>
     </row>
     <row r="49">
@@ -2374,25 +2374,25 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.307436</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.113218</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.287901</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.487673</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.483362</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.204802</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.204802</v>
       </c>
     </row>
     <row r="71">
@@ -2402,25 +2402,25 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>1.103438</v>
+        <v>1.410874</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1.486136</v>
+        <v>1.599354</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1.109713</v>
+        <v>1.397614</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>8.634258000000001</v>
+        <v>9.121931</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.019812</v>
+        <v>0.503174</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>15.988401</v>
+        <v>16.193203</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>15.988401</v>
+        <v>16.193203</v>
       </c>
     </row>
     <row r="72">
@@ -2514,25 +2514,25 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>3.34295</v>
+        <v>3.035514</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.69427</v>
+        <v>1.581052</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>8.544816000000001</v>
+        <v>8.256914999999999</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.600499</v>
+        <v>2.112826</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2.564697</v>
+        <v>2.081335</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1.924212</v>
+        <v>1.71941</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.924212</v>
+        <v>1.71941</v>
       </c>
     </row>
     <row r="76">
@@ -2654,25 +2654,25 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>3.442207315738093</v>
+        <v>3.581285777748423</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.6886010435754378</v>
+        <v>0.6943230549429433</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.5934397148191014</v>
+        <v>0.6064730675009432</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.5532086674196994</v>
+        <v>0.5843830085639896</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.148304043109923</v>
+        <v>2.226580047798432</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>57.01916163820773</v>
+        <v>57.74954351578437</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>-1.409063981251494</v>
+        <v>-1.427113260944208</v>
       </c>
     </row>
     <row r="81">
@@ -3364,22 +3364,22 @@
         <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-0.7732869999999999</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-2.002506</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>1.395097</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>1.871341</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.042439</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.73415</v>
       </c>
     </row>
     <row r="107">
@@ -5206,7 +5206,11 @@
           <t>Current portion of lease obligations (note 18, 20) 417,619</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -6606,7 +6610,11 @@
           <t>Current portion of lease obligations (note 18)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -9501,7 +9509,11 @@
           <t>Current portion of lease obligations (note 20)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -10794,7 +10806,11 @@
           <t>Current portion of lease obligations (note 19)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>0.307436</v>
       </c>
@@ -12032,7 +12048,11 @@
           <t>Current portion of lease obligations (note 18, 20)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -13165,7 +13185,11 @@
           <t>Net changes in non-cash operating working capital (note 12)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -15520,7 +15544,11 @@
           <t>Changes in non-cash operating working capital (note 12)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -17061,7 +17089,11 @@
           <t>Changes in non-cash operating working capital (note 14)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -22440,7 +22472,11 @@
           <t>Deferred income tax recovery (note 19)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -23903,7 +23939,11 @@
           <t>Income tax recovery (note 19)</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -25730,7 +25770,11 @@
           <t>Current income tax (recovery) expense (note 21)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -25777,7 +25821,11 @@
           <t>Deferred income tax (recovery) expense (note 21)</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -25824,7 +25872,11 @@
           <t>Income tax (recovery) expense (note 21)</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -27932,7 +27984,11 @@
           <t>Deferred income tax recovery (expense) (note 20)</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E475" s="5" t="n">
         <v>-0.005575</v>
       </c>
